--- a/excelAvancado/aula01/Base de Dados - Atividade Diagnóstica.xlsx
+++ b/excelAvancado/aula01/Base de Dados - Atividade Diagnóstica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professor\Documents\Excel Avançado\Aula 01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\excelAvancado\aula01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36467C75-6598-4F24-9A11-F55A4EDE2578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6FED72-AF33-4FA9-8FF3-2C63DB31053E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11040" xr2:uid="{50CEBCFD-DA60-4D40-B497-E1EF5C83A109}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{50CEBCFD-DA60-4D40-B497-E1EF5C83A109}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,25 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Produto A</t>
-  </si>
-  <si>
-    <t>25.37</t>
   </si>
   <si>
     <t>PA-123</t>
@@ -39,22 +47,13 @@
     <t>Produto B</t>
   </si>
   <si>
-    <t>30.82</t>
-  </si>
-  <si>
     <t>PB-456</t>
   </si>
   <si>
     <t>Produto C</t>
   </si>
   <si>
-    <t>20.15</t>
-  </si>
-  <si>
     <t>Produto D</t>
-  </si>
-  <si>
-    <t>35.91</t>
   </si>
   <si>
     <t>PA-987</t>
@@ -63,16 +62,10 @@
     <t>Produto E</t>
   </si>
   <si>
-    <t>28.48</t>
-  </si>
-  <si>
     <t>PB-654</t>
   </si>
   <si>
     <t>Produto F</t>
-  </si>
-  <si>
-    <t>22.76</t>
   </si>
   <si>
     <t>PA-321</t>
@@ -81,14 +74,47 @@
     <t>Produto G</t>
   </si>
   <si>
-    <t>23.50</t>
+    <t>Nome do Produto</t>
+  </si>
+  <si>
+    <t>Quantidade Vendida</t>
+  </si>
+  <si>
+    <t>Preço Unitário</t>
+  </si>
+  <si>
+    <t>Código do Produto</t>
+  </si>
+  <si>
+    <t>Faturamento</t>
+  </si>
+  <si>
+    <t>Total Vendido</t>
+  </si>
+  <si>
+    <t>Media Preço Unitário</t>
+  </si>
+  <si>
+    <t>Menor Preço Unit.</t>
+  </si>
+  <si>
+    <t>Maior Preço Unit</t>
+  </si>
+  <si>
+    <t>Arrendondar média Preço Unit.</t>
+  </si>
+  <si>
+    <t>Codigos Preenchidos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,16 +122,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -113,14 +166,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -136,10 +235,1953 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Faturamento por</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" baseline="0"/>
+              <a:t> Produto</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Produto A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Produto B</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Produto C</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Produto D</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Produto E</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Produto F</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Produto G</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$E$2:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>253.70000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>462.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>403</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>430.91999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>512.64</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500.72</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>235</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-21C0-41A4-BD16-757FE04ADCCE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="700439136"/>
+        <c:axId val="616960592"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="700439136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="616960592"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="616960592"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="700439136"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>% de participação</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-366C-42D0-8440-D07A4C97BA6B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-366C-42D0-8440-D07A4C97BA6B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-366C-42D0-8440-D07A4C97BA6B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-366C-42D0-8440-D07A4C97BA6B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-366C-42D0-8440-D07A4C97BA6B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-366C-42D0-8440-D07A4C97BA6B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-366C-42D0-8440-D07A4C97BA6B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Produto A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Produto B</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Produto C</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Produto D</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Produto E</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Produto F</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Produto G</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$E$2:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>253.70000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>462.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>403</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>430.91999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>512.64</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500.72</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>235</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3175-4331-A514-C498AFB22D66}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>222249</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03935E09-99A1-5404-EA07-170F072388F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3492B55-6876-0078-E6CF-715A7EE3AF7F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +2219,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -283,7 +2325,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -425,7 +2467,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -433,108 +2475,211 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2A0D8C0-707C-4D2B-B6EB-812F4C12AA90}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B2" s="4">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" s="5">
+        <v>25.37</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E2" s="6">
+        <f>PRODUCT(B2,C2)</f>
+        <v>253.70000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="B3" s="4">
+        <v>15</v>
+      </c>
+      <c r="C3" s="5">
+        <v>30.82</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="6">
+        <f t="shared" ref="E3:E8" si="0">PRODUCT(B3,C3)</f>
+        <v>462.3</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B4" s="4">
+        <v>20</v>
+      </c>
+      <c r="C4" s="5">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="6">
+        <f t="shared" si="0"/>
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="B5" s="4">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5">
+        <v>35.909999999999997</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" si="0"/>
+        <v>430.91999999999996</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5">
+        <v>28.48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="shared" si="0"/>
+        <v>512.64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5">
+        <v>22.76</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="6">
+        <f t="shared" si="0"/>
+        <v>500.72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5">
+        <v>23.5</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="6">
+        <f t="shared" si="0"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="4">
+        <f>SUM(B2:B8)</f>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="7">
+        <f>AVERAGE(C2:C8)</f>
+        <v>26.712857142857139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="7">
+        <f>MIN(C2:C8)</f>
+        <v>20.149999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
+      <c r="B14" s="7">
+        <f>MAX(C2:C8)</f>
+        <v>35.909999999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="7">
+        <f>ROUND(AVERAGE(C2:C8),0)</f>
+        <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
+      <c r="B16" s="8">
+        <f>COUNTA(D2:D8)</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>